--- a/src/main/java/com/uem_automation/qa/testdata/UEM_AUTOMATION_TESTDATA.xlsx
+++ b/src/main/java/com/uem_automation/qa/testdata/UEM_AUTOMATION_TESTDATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - CYBERCORP LIMITED\Projects\intellij-workspace\UEM_AUTOAMATION_V3\src\main\java\com\uem_automation\qa\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - CYBERCORP LIMITED\Projects\intellij-workspace\UEM_AUTOMATION_TESTNG_FRAMEWORK\src\main\java\com\uem_automation\qa\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{E2D6B881-A3D2-4649-8872-7E2B39C8D339}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{99DB0EEB-50C3-41E0-A7E6-B4E8E05FA710}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D5112858B5AB48CE35E55F9A3B3C6A04DE4AEEA9" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7B2351-8842-4E91-BFE8-179D93150EFE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8550" firstSheet="34" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000" firstSheet="40" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -68,16 +68,22 @@
     <sheet name="ImportFile" sheetId="58" r:id="rId53"/>
     <sheet name="SoftwarePatchInstallUninstall" sheetId="24" r:id="rId54"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId55"/>
+    <sheet name="Sheet2" sheetId="59" r:id="rId56"/>
   </sheets>
   <definedNames>
     <definedName name="MasterTemplate">Template!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="519">
   <si>
     <t>Email</t>
   </si>
@@ -88,15 +94,18 @@
     <t>Select View</t>
   </si>
   <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>Default View - Device Manager</t>
+  </si>
+  <si>
     <t>prajwal</t>
   </si>
   <si>
     <t>pass_123</t>
   </si>
   <si>
-    <t>Default View - Device Manager</t>
-  </si>
-  <si>
     <t>pankaj.wairagade@vdi.com</t>
   </si>
   <si>
@@ -112,9 +121,6 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
     <t>xyz</t>
   </si>
   <si>
@@ -145,7 +151,7 @@
     <t>Display Time</t>
   </si>
   <si>
-    <t>A101_UEM_Automation_Template</t>
+    <t>A102_UEM_Automation_Template</t>
   </si>
   <si>
     <t>Windows</t>
@@ -202,1462 +208,1450 @@
     <t>AES</t>
   </si>
   <si>
+    <t>vdi.com</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>User Authentication</t>
+  </si>
+  <si>
+    <t>TKIP</t>
+  </si>
+  <si>
+    <t>test domain username</t>
+  </si>
+  <si>
+    <t>test domain password</t>
+  </si>
+  <si>
+    <t>802.1X</t>
+  </si>
+  <si>
+    <t>WEP</t>
+  </si>
+  <si>
+    <t>Ethernet Network</t>
+  </si>
+  <si>
+    <t>Select Tab</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>Postfix</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>No Of Char</t>
+  </si>
+  <si>
+    <t>Computer Name Username</t>
+  </si>
+  <si>
+    <t>Computer Name Password</t>
+  </si>
+  <si>
+    <t>Radio Type</t>
+  </si>
+  <si>
+    <t>Organizational Unit</t>
+  </si>
+  <si>
+    <t>Work Group Name</t>
+  </si>
+  <si>
+    <t>Workgroup Username</t>
+  </si>
+  <si>
+    <t>Workgroup Password</t>
+  </si>
+  <si>
+    <t>ComputerName</t>
+  </si>
+  <si>
+    <t>UnifiedXprefix</t>
+  </si>
+  <si>
+    <t>postfixTM</t>
+  </si>
+  <si>
+    <t>Mac Address</t>
+  </si>
+  <si>
+    <t>asit</t>
+  </si>
+  <si>
+    <t>asit#123</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>computers</t>
+  </si>
+  <si>
+    <t>Workgroup</t>
+  </si>
+  <si>
+    <t>WORKGROUP</t>
+  </si>
+  <si>
+    <t>Ethernet Type</t>
+  </si>
+  <si>
+    <t>Obtain DNS Server Address Automatically</t>
+  </si>
+  <si>
+    <t>Primary DNS</t>
+  </si>
+  <si>
+    <t>Secondary DNS</t>
+  </si>
+  <si>
+    <t>DHCP</t>
+  </si>
+  <si>
+    <t>192.168.10.1</t>
+  </si>
+  <si>
+    <t>Network SSID</t>
+  </si>
+  <si>
+    <t>Network Key</t>
+  </si>
+  <si>
+    <t>Connect If Network In Range</t>
+  </si>
+  <si>
+    <t>Connect If Network Is Not Broadcasting</t>
+  </si>
+  <si>
+    <t>WP1-5G</t>
+  </si>
+  <si>
+    <t>WPA2-Personal</t>
+  </si>
+  <si>
+    <t>CCL#123$</t>
+  </si>
+  <si>
+    <t>Wireless Type</t>
+  </si>
+  <si>
+    <t>Display Resolution</t>
+  </si>
+  <si>
+    <t>Color Depth</t>
+  </si>
+  <si>
+    <t>Dual Display</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
+    <t>1024 X 768 @ 60 Hz</t>
+  </si>
+  <si>
+    <t>Largest (32-bit)</t>
+  </si>
+  <si>
+    <t>Disabled</t>
+  </si>
+  <si>
+    <t>Extended</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>90°</t>
+  </si>
+  <si>
+    <t>Keyboard Locales</t>
+  </si>
+  <si>
+    <t>Replace All Existing Keyboard</t>
+  </si>
+  <si>
+    <t>English (United States)</t>
+  </si>
+  <si>
+    <t>French (Switzerland)</t>
+  </si>
+  <si>
+    <t>Left Hand Configuration</t>
+  </si>
+  <si>
+    <t>Power Plan</t>
+  </si>
+  <si>
+    <t>Turn Off The Display</t>
+  </si>
+  <si>
+    <t>Put The Computer To Sleep</t>
+  </si>
+  <si>
+    <t>Balanced</t>
+  </si>
+  <si>
+    <t>Never</t>
+  </si>
+  <si>
+    <t>Power saver</t>
+  </si>
+  <si>
+    <t>5 Minutes</t>
+  </si>
+  <si>
+    <t>Port Type</t>
+  </si>
+  <si>
+    <t>Printer Name</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Printer Driver List</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>Port Text</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>isShared</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Ms Printer</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Microsoft OpenXPS Class Driver 2</t>
+  </si>
+  <si>
+    <t>COM1 :(Serial Port)</t>
+  </si>
+  <si>
+    <t>IP Port</t>
+  </si>
+  <si>
+    <t>Network Printer</t>
+  </si>
+  <si>
+    <t>\\192.168.2.52\HPPrinter</t>
+  </si>
+  <si>
+    <t>Vinayak</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>Time Server</t>
+  </si>
+  <si>
+    <t>Date Time</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>(UTC+05:30) Chennai, Kolkata, Mumbai, New Delhi</t>
+  </si>
+  <si>
+    <t>time.nist.gov</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Date Separator</t>
+  </si>
+  <si>
+    <t>Short Date Format</t>
+  </si>
+  <si>
+    <t>Long Date Format</t>
+  </si>
+  <si>
+    <t>Time Format</t>
+  </si>
+  <si>
+    <t>Region &amp; Location</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>English - India</t>
+  </si>
+  <si>
+    <t>Date &amp; Time Format</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>dd/MMM/yy</t>
+  </si>
+  <si>
+    <t>dddd, dd MMMM, yyyy</t>
+  </si>
+  <si>
+    <t>h:mm:ss tt</t>
+  </si>
+  <si>
+    <t>Application Path</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>AlertUser</t>
+  </si>
+  <si>
+    <t>Message Type</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Required Command Output</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>C:\Program Files\Google\Chrome\Application\chrome.exe</t>
+  </si>
+  <si>
+    <t>incognito</t>
+  </si>
+  <si>
+    <t>Message box</t>
+  </si>
+  <si>
+    <t>Application launch</t>
+  </si>
+  <si>
+    <t>test message</t>
+  </si>
+  <si>
+    <t>2 Minute</t>
+  </si>
+  <si>
+    <t>C:\Windows\System32\cleanmgr.exe</t>
+  </si>
+  <si>
+    <t>testdata parameters</t>
+  </si>
+  <si>
+    <t>Information message box</t>
+  </si>
+  <si>
+    <t>test title</t>
+  </si>
+  <si>
+    <t>1 Minute</t>
+  </si>
+  <si>
+    <t>getmac</t>
+  </si>
+  <si>
+    <t>ipconfig</t>
+  </si>
+  <si>
+    <t>5 Seconds</t>
+  </si>
+  <si>
+    <t>Variable Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>mmc</t>
+  </si>
+  <si>
+    <t>C:\Windows\System32\mmc.exe</t>
+  </si>
+  <si>
+    <t>Browser Installed</t>
+  </si>
+  <si>
+    <t>Forcefully Close The Browser Instance</t>
+  </si>
+  <si>
+    <t>Internet Browser Cookies</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Temporary Internet Files</t>
+  </si>
+  <si>
+    <t>Clear The Recent Document History</t>
+  </si>
+  <si>
+    <t>Clear The Start Menu Run History</t>
+  </si>
+  <si>
+    <t>Clear The Find Files History</t>
+  </si>
+  <si>
+    <t>Clear The MS Paint Recent File History</t>
+  </si>
+  <si>
+    <t>Clear The MS Wordpad Recent File History</t>
+  </si>
+  <si>
+    <t>Clear The Command Dialogue Open Save History</t>
+  </si>
+  <si>
+    <t>Clear The Command Dialogue Last Visited Folder History</t>
+  </si>
+  <si>
+    <t>Please Empty The Clipboard</t>
+  </si>
+  <si>
+    <t>Empty The Recycle Bin</t>
+  </si>
+  <si>
+    <t>Delete Windows Temporary Files</t>
+  </si>
+  <si>
+    <t>Web Browser</t>
+  </si>
+  <si>
+    <t>Google Chrome</t>
+  </si>
+  <si>
+    <t>Internet Explorer</t>
+  </si>
+  <si>
+    <t>Windows Cleaner</t>
+  </si>
+  <si>
+    <t>Registry Key User</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Backup Path</t>
+  </si>
+  <si>
+    <t>Backup Name</t>
+  </si>
+  <si>
+    <t>Obtain Registry</t>
+  </si>
+  <si>
+    <t>HKEY_USERS</t>
+  </si>
+  <si>
+    <t>WOW6432Node\RemoteApps\RemoteSettings</t>
+  </si>
+  <si>
+    <t>Registry Backup</t>
+  </si>
+  <si>
+    <t>C:\</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> backup Registry</t>
+  </si>
+  <si>
+    <t>Application Name</t>
+  </si>
+  <si>
+    <t>isEnabled</t>
+  </si>
+  <si>
+    <t>C:\Windows\System32\cmd.exe</t>
+  </si>
+  <si>
+    <t>cmd.exe</t>
+  </si>
+  <si>
+    <t>C:\Windows\System32\notepad.exe</t>
+  </si>
+  <si>
+    <t>notepad.exe</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>MicrosoftEdgeUpdateTaskMachineCore</t>
+  </si>
+  <si>
+    <t>Task Reboot Monitoring</t>
+  </si>
+  <si>
+    <t>DHCP Discovery</t>
+  </si>
+  <si>
+    <t>Monitoring and Maintainance</t>
+  </si>
+  <si>
+    <t>Battery Indicator</t>
+  </si>
+  <si>
+    <t>Idle State</t>
+  </si>
+  <si>
+    <t>Config Sync</t>
+  </si>
+  <si>
+    <t>BootLog</t>
+  </si>
+  <si>
+    <t>Usb Mass Storage Logs</t>
+  </si>
+  <si>
+    <t>Screen Saver Logs</t>
+  </si>
+  <si>
+    <t>Enable Vnc Acceptance</t>
+  </si>
+  <si>
+    <t>Sync Task Scheduler</t>
+  </si>
+  <si>
+    <t>Application Log</t>
+  </si>
+  <si>
+    <t>Cpu Utilization Log</t>
+  </si>
+  <si>
+    <t>Write Filter Logs</t>
+  </si>
+  <si>
+    <t>SignalR Monitoring</t>
+  </si>
+  <si>
+    <t>Hardware Logs</t>
+  </si>
+  <si>
+    <t>Enable Agent Debug Logs</t>
+  </si>
+  <si>
+    <t>Download Attempts</t>
+  </si>
+  <si>
+    <t>Location Range</t>
+  </si>
+  <si>
+    <t>Hardware Logs Interval</t>
+  </si>
+  <si>
+    <t>Heart Beat Interval</t>
+  </si>
+  <si>
+    <t>SignalR Connection Path</t>
+  </si>
+  <si>
+    <t>User Level</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>/communication/signalr/hubs</t>
+  </si>
+  <si>
+    <t>Developer Level</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>VNC Password</t>
+  </si>
+  <si>
+    <t>Server IP Name</t>
+  </si>
+  <si>
+    <t>Port Number</t>
+  </si>
+  <si>
+    <t>winserver.vdi.com</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Startup Type</t>
+  </si>
+  <si>
+    <t>Microsoft App-V Client</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Automatic</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>RESTART</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>USB Device Controller Status</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>Audio/Video</t>
+  </si>
+  <si>
+    <t>Human Interface</t>
+  </si>
+  <si>
+    <t>Image Devices</t>
+  </si>
+  <si>
+    <t>Mass Storage</t>
+  </si>
+  <si>
+    <t>Printers</t>
+  </si>
+  <si>
+    <t>Smart Card Reader</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Wireless Controllers</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Member Of</t>
+  </si>
+  <si>
+    <t>User Can Not Change The Password</t>
+  </si>
+  <si>
+    <t>Password Never Expires</t>
+  </si>
+  <si>
+    <t>Disable User</t>
+  </si>
+  <si>
+    <t>Add User</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin@123</t>
+  </si>
+  <si>
+    <t>test user</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin </t>
+  </si>
+  <si>
+    <t>Reset User</t>
+  </si>
+  <si>
+    <t>000000</t>
+  </si>
+  <si>
+    <t>Write Filter Setting</t>
+  </si>
+  <si>
+    <t>Write Filter</t>
+  </si>
+  <si>
+    <t>File And Folder Path</t>
+  </si>
+  <si>
+    <t>Registry Path</t>
+  </si>
+  <si>
+    <t>Set Max Cache Size For Next Session</t>
+  </si>
+  <si>
+    <t>Overlay Size</t>
+  </si>
+  <si>
+    <t>Alert User</t>
+  </si>
+  <si>
+    <t>Message Important</t>
+  </si>
+  <si>
+    <t>Disable Write Filter</t>
+  </si>
+  <si>
+    <t>Write Filter Exclusion List</t>
+  </si>
+  <si>
+    <t>Enable UWF</t>
+  </si>
+  <si>
+    <t>HKEY_LOCAL_MACHINE\SOFTWARE\policies\chrome</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Message from Administrator</t>
+  </si>
+  <si>
+    <t>A maintenance task is going to be performed on your desktop. Your device may Shutdown to complete the task, so you need to save any open work to avoid data loss and then press ok</t>
+  </si>
+  <si>
+    <t>FBWF Cache Size</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Overlay Settings</t>
+  </si>
+  <si>
+    <t>Select Protocol</t>
+  </si>
+  <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Program Path</t>
+  </si>
+  <si>
+    <t>Add Port</t>
+  </si>
+  <si>
+    <t>TcpPort</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>UdpPort</t>
+  </si>
+  <si>
+    <t>UDP</t>
+  </si>
+  <si>
+    <t>Add Program</t>
+  </si>
+  <si>
+    <t>testprogramname</t>
+  </si>
+  <si>
+    <t>C:\Program Files\Internet Explorer\iexplore.exe</t>
+  </si>
+  <si>
+    <t>Automatically Detect Settings</t>
+  </si>
+  <si>
+    <t>Use Automatic Configuration Script</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Installation &amp; Uninstallation Restriction</t>
+  </si>
+  <si>
+    <t>Software Restriction</t>
+  </si>
+  <si>
+    <t>Software Application  Name</t>
+  </si>
+  <si>
+    <t>Browser Name</t>
+  </si>
+  <si>
+    <t>Restriction Type</t>
+  </si>
+  <si>
+    <t>Installation &amp; Uninstallation</t>
+  </si>
+  <si>
+    <t>Application Restriction</t>
+  </si>
+  <si>
+    <t>Allow All</t>
+  </si>
+  <si>
+    <t>PDF Viewer</t>
+  </si>
+  <si>
+    <t>Deny All</t>
+  </si>
+  <si>
+    <t>Citrix Workspace</t>
+  </si>
+  <si>
+    <t>Browser Restriction</t>
+  </si>
+  <si>
+    <t>Block all downloads</t>
+  </si>
+  <si>
+    <t>File Folder</t>
+  </si>
+  <si>
+    <t>C:\Users\Administrator\Desktop</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>ConnectionName</t>
+  </si>
+  <si>
+    <t>Certificate Type</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>Store Name</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>New Upload</t>
+  </si>
+  <si>
+    <t>FDM_HTTP</t>
+  </si>
+  <si>
+    <t>CER</t>
+  </si>
+  <si>
+    <t>ShradhaCerFile.cer</t>
+  </si>
+  <si>
+    <t>Personal certificates</t>
+  </si>
+  <si>
+    <t>PFX</t>
+  </si>
+  <si>
+    <t>ShradhaPexFile.pfx</t>
+  </si>
+  <si>
+    <t>Trusted Publishers</t>
+  </si>
+  <si>
+    <t>FTPS</t>
+  </si>
+  <si>
+    <t>Repository</t>
+  </si>
+  <si>
+    <t>$GROUP$</t>
+  </si>
+  <si>
+    <t>Enable CD DVD</t>
+  </si>
+  <si>
+    <t>Bluetooth Device</t>
+  </si>
+  <si>
+    <t>Enable</t>
+  </si>
+  <si>
+    <t>Disable</t>
+  </si>
+  <si>
+    <t>Enable Firewall</t>
+  </si>
+  <si>
+    <t>Enable Parallel Port</t>
+  </si>
+  <si>
+    <t>Enable Serial Port</t>
+  </si>
+  <si>
+    <t>Enable USB Port</t>
+  </si>
+  <si>
+    <t>USB Mass Storage</t>
+  </si>
+  <si>
+    <t>USB Write Protect</t>
+  </si>
+  <si>
+    <t>Connection Name</t>
+  </si>
+  <si>
+    <t>Citrix Type</t>
+  </si>
+  <si>
+    <t>Configuration URL</t>
+  </si>
+  <si>
+    <t>Citrix01</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>StoreNew</t>
+  </si>
+  <si>
+    <t>https://xd718server.vdi.com</t>
+  </si>
+  <si>
+    <t>Template manager</t>
+  </si>
+  <si>
+    <t>TestCitrix01</t>
+  </si>
+  <si>
+    <t>PNA</t>
+  </si>
+  <si>
+    <t>https://192.168.1.23/Citrix/PNAgent/Config.xml</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Create Shortcut On Desktop</t>
+  </si>
+  <si>
+    <t>Auto Start Connection</t>
+  </si>
+  <si>
+    <t>Arguments</t>
+  </si>
+  <si>
+    <t>PaintConnection</t>
+  </si>
+  <si>
+    <t>C:\Windows\System32\mspaint.exe</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>ConnectionChrome</t>
+  </si>
+  <si>
+    <t>Browser Type</t>
+  </si>
+  <si>
+    <t>Kiosk Mode</t>
+  </si>
+  <si>
+    <t>Auto Reconnect Connection</t>
+  </si>
+  <si>
+    <t>BrowserChrome</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>http://www.google.com</t>
+  </si>
+  <si>
+    <t>BrowserEdge</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>http://www.gmail.com</t>
+  </si>
+  <si>
+    <t>IP Host Name</t>
+  </si>
+  <si>
+    <t>Always Ask For Cred</t>
+  </si>
+  <si>
+    <t>Automatic Logon</t>
+  </si>
+  <si>
+    <t>Automatic Start</t>
+  </si>
+  <si>
+    <t>Use All Monitors For Remote Session</t>
+  </si>
+  <si>
+    <t>Full Screen</t>
+  </si>
+  <si>
+    <t>Size Of Desktop</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Display Connection Bar</t>
+  </si>
+  <si>
+    <t>Remote Audio Playback</t>
+  </si>
+  <si>
+    <t>Remote Audio Recording</t>
+  </si>
+  <si>
+    <t>Drives</t>
+  </si>
+  <si>
+    <t>Clipboard</t>
+  </si>
+  <si>
+    <t>Smart Cards</t>
+  </si>
+  <si>
+    <t>Ports</t>
+  </si>
+  <si>
+    <t>PNP Devices</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Start Program On Connection</t>
+  </si>
+  <si>
+    <t>Program Path File Name</t>
+  </si>
+  <si>
+    <t>Start In Following Folder</t>
+  </si>
+  <si>
+    <t>Connection Speed</t>
+  </si>
+  <si>
+    <t>Reconnect If Connection Dropped</t>
+  </si>
+  <si>
+    <t>Authentication Option</t>
+  </si>
+  <si>
+    <t>Do Not Use RD Gateway</t>
+  </si>
+  <si>
+    <t>testConnection</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>192.168.3.138</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>1024x768</t>
+  </si>
+  <si>
+    <t>High Color(16 bit)</t>
+  </si>
+  <si>
+    <t>True Color(24 bit)</t>
+  </si>
+  <si>
+    <t>Local Resources</t>
+  </si>
+  <si>
+    <t>Do not play</t>
+  </si>
+  <si>
+    <t>Do not record</t>
+  </si>
+  <si>
+    <t>On the remote computer</t>
+  </si>
+  <si>
+    <t>Programs</t>
+  </si>
+  <si>
+    <t>D:\sample\sample.exe</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>LAN(10 Mbps or higher)</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Warn me</t>
+  </si>
+  <si>
+    <t>Host Name</t>
+  </si>
+  <si>
+    <t>Remote work station card</t>
+  </si>
+  <si>
+    <t>Usb Disable</t>
+  </si>
+  <si>
+    <t>Create Shortcut in the start menu</t>
+  </si>
+  <si>
+    <t>Teradici PCoIP</t>
+  </si>
+  <si>
+    <t>vdi</t>
+  </si>
+  <si>
+    <t>Windowed</t>
+  </si>
+  <si>
+    <t>Fullscreen</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Application or Desktop Name</t>
+  </si>
+  <si>
+    <t>Smart Card Pin</t>
+  </si>
+  <si>
+    <t>Connect Usb On Startup</t>
+  </si>
+  <si>
+    <t>Connect Usb On Insert</t>
+  </si>
+  <si>
+    <t>Non Interactive</t>
+  </si>
+  <si>
+    <t>Reconnect Behaviour</t>
+  </si>
+  <si>
+    <t>VMW Protocol</t>
+  </si>
+  <si>
+    <t>chrome.exe</t>
+  </si>
+  <si>
+    <t>Reconnect automatically to open applications</t>
+  </si>
+  <si>
+    <t>RDP protocol setting</t>
+  </si>
+  <si>
+    <t>Desktop Name</t>
+  </si>
+  <si>
+    <t>Unauthenticated Access</t>
+  </si>
+  <si>
+    <t>Hide Client After Launch</t>
+  </si>
+  <si>
+    <t>Allow H264 Decoding</t>
+  </si>
+  <si>
+    <t>Allow High Color Accuracy</t>
+  </si>
+  <si>
+    <t>Configure SSL</t>
+  </si>
+  <si>
+    <t>Network Condition</t>
+  </si>
+  <si>
+    <t>Never connect to untrusted server</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Do not verify server identity certificates</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Disable Client Save</t>
+  </si>
+  <si>
+    <t>Lock Computer Save</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>Feedback</t>
+  </si>
+  <si>
+    <t>Message from Admin</t>
+  </si>
+  <si>
+    <t>Service Mode</t>
+  </si>
+  <si>
+    <t>Enabled Service Mode</t>
+  </si>
+  <si>
+    <t>Disabled Service Mode</t>
+  </si>
+  <si>
+    <t>Shut Down</t>
+  </si>
+  <si>
+    <t>Inventory Sync</t>
+  </si>
+  <si>
+    <t>Hardware &amp; Software Inventory(Windows)</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Wake On Lan Save</t>
+  </si>
+  <si>
+    <t>Target Folder Path</t>
+  </si>
+  <si>
+    <t>Source Type</t>
+  </si>
+  <si>
+    <t>Global Repository</t>
+  </si>
+  <si>
+    <t>Execute File</t>
+  </si>
+  <si>
+    <t>Batch Execution</t>
+  </si>
+  <si>
+    <t>Command Parameter</t>
+  </si>
+  <si>
+    <t>File Transfer</t>
+  </si>
+  <si>
+    <t>Upload</t>
+  </si>
+  <si>
+    <t>ChromeSetup.exe</t>
+  </si>
+  <si>
+    <t>test command</t>
+  </si>
+  <si>
+    <t>Folder Transfer</t>
+  </si>
+  <si>
+    <t>C:\Program Files (x86)\LogsDir\Connections</t>
+  </si>
+  <si>
+    <t>FolderTransferFiles.zip</t>
+  </si>
+  <si>
+    <t>sample-1.zip</t>
+  </si>
+  <si>
+    <t>File Path</t>
+  </si>
+  <si>
+    <t>Folder Path</t>
+  </si>
+  <si>
+    <t>Folder Synchronization Path</t>
+  </si>
+  <si>
+    <t>Import File</t>
+  </si>
+  <si>
+    <t>C:\Program Files (x86)\LogsDir\DeveloperLog.log</t>
+  </si>
+  <si>
+    <t>Import Folder</t>
+  </si>
+  <si>
+    <t>Folder synchronization</t>
+  </si>
+  <si>
+    <t>Select New Install Or Uninstall</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>NEW INSTALL</t>
+  </si>
+  <si>
+    <t>/quiet</t>
+  </si>
+  <si>
+    <t>2XClient.msi</t>
+  </si>
+  <si>
+    <t>$Group$</t>
+  </si>
+  <si>
+    <t>testingpr1</t>
+  </si>
+  <si>
+    <t>testingpr2</t>
+  </si>
+  <si>
+    <t>demo postponement message</t>
+  </si>
+  <si>
+    <t>testingpr3</t>
+  </si>
+  <si>
+    <t>Asynchronous</t>
+  </si>
+  <si>
+    <t>testingpr4</t>
+  </si>
+  <si>
+    <t>testingpr5</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>testingpr6</t>
+  </si>
+  <si>
+    <t>testingpr7</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>testingpr8</t>
+  </si>
+  <si>
+    <t>testingpr9</t>
+  </si>
+  <si>
+    <t>IOS</t>
+  </si>
+  <si>
+    <t>testingpr10</t>
+  </si>
+  <si>
     <t>test domain name</t>
   </si>
   <si>
-    <t>test domain username</t>
-  </si>
-  <si>
-    <t>test domain password</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>User Authentication</t>
-  </si>
-  <si>
-    <t>TKIP</t>
-  </si>
-  <si>
-    <t>802.1X</t>
-  </si>
-  <si>
-    <t>WEP</t>
-  </si>
-  <si>
-    <t>Ethernet Network</t>
-  </si>
-  <si>
-    <t>Select Tab</t>
-  </si>
-  <si>
-    <t>Prefix</t>
-  </si>
-  <si>
-    <t>Postfix</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>No Of Char</t>
-  </si>
-  <si>
-    <t>Computer Name Username</t>
-  </si>
-  <si>
-    <t>Computer Name Password</t>
-  </si>
-  <si>
-    <t>Radio Type</t>
-  </si>
-  <si>
-    <t>Organizational Unit</t>
-  </si>
-  <si>
-    <t>Work Group Name</t>
-  </si>
-  <si>
-    <t>Workgroup Username</t>
-  </si>
-  <si>
-    <t>Workgroup Password</t>
-  </si>
-  <si>
-    <t>ComputerName</t>
-  </si>
-  <si>
-    <t>prefix_testdata</t>
-  </si>
-  <si>
-    <t>postfix_testdata</t>
-  </si>
-  <si>
-    <t>Mac Address</t>
-  </si>
-  <si>
-    <t>comp name testdata</t>
-  </si>
-  <si>
-    <t>comp password testdata</t>
-  </si>
-  <si>
-    <t>Domain</t>
-  </si>
-  <si>
-    <t>testUnit</t>
-  </si>
-  <si>
-    <t>prajwal usr</t>
-  </si>
-  <si>
-    <t>prajwal pass</t>
-  </si>
-  <si>
-    <t>Workgroup</t>
-  </si>
-  <si>
-    <t>WORKGROUP</t>
-  </si>
-  <si>
-    <t>test work group username</t>
-  </si>
-  <si>
-    <t>test work group password</t>
-  </si>
-  <si>
-    <t>Ethernet Type</t>
-  </si>
-  <si>
-    <t>Obtain DNS Server Address Automatically</t>
-  </si>
-  <si>
-    <t>Primary DNS</t>
-  </si>
-  <si>
-    <t>Secondary DNS</t>
-  </si>
-  <si>
-    <t>DHCP</t>
-  </si>
-  <si>
-    <t>192.168.10.1</t>
-  </si>
-  <si>
-    <t>Network SSID</t>
-  </si>
-  <si>
-    <t>Network Key</t>
-  </si>
-  <si>
-    <t>Connect If Network In Range</t>
-  </si>
-  <si>
-    <t>Connect If Network Is Not Broadcasting</t>
-  </si>
-  <si>
-    <t>WP1-5G</t>
-  </si>
-  <si>
-    <t>WPA2-Personal</t>
-  </si>
-  <si>
-    <t>CCL#123$</t>
-  </si>
-  <si>
-    <t>Wireless Type</t>
-  </si>
-  <si>
-    <t>Display Resolution</t>
-  </si>
-  <si>
-    <t>Color Depth</t>
-  </si>
-  <si>
-    <t>Dual Display</t>
-  </si>
-  <si>
-    <t>Rotation</t>
-  </si>
-  <si>
-    <t>1024 X 768 @ 60 Hz</t>
-  </si>
-  <si>
-    <t>Largest (32-bit)</t>
-  </si>
-  <si>
-    <t>Disabled</t>
-  </si>
-  <si>
-    <t>Extended</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>90°</t>
-  </si>
-  <si>
-    <t>Keyboard Locales</t>
-  </si>
-  <si>
-    <t>Replace All Existing Keyboard</t>
-  </si>
-  <si>
-    <t>English (United States)</t>
-  </si>
-  <si>
-    <t>French (Switzerland)</t>
-  </si>
-  <si>
-    <t>Left Hand Configuration</t>
-  </si>
-  <si>
-    <t>Power Plan</t>
-  </si>
-  <si>
-    <t>Turn Off The Display</t>
-  </si>
-  <si>
-    <t>Put The Computer To Sleep</t>
-  </si>
-  <si>
-    <t>Balanced</t>
-  </si>
-  <si>
-    <t>Never</t>
-  </si>
-  <si>
-    <t>Power saver</t>
-  </si>
-  <si>
-    <t>2 Minutes</t>
-  </si>
-  <si>
-    <t>Port Type</t>
-  </si>
-  <si>
-    <t>Printer Name</t>
-  </si>
-  <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Printer Driver List</t>
-  </si>
-  <si>
-    <t>Port</t>
-  </si>
-  <si>
-    <t>IP Address</t>
-  </si>
-  <si>
-    <t>Port Text</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>isShared</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Ms Printer</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Microsoft OpenXPS Class Driver 2</t>
-  </si>
-  <si>
-    <t>COM1 :(Serial Port)</t>
-  </si>
-  <si>
-    <t>IP Port</t>
-  </si>
-  <si>
-    <t>Network Printer</t>
-  </si>
-  <si>
-    <t>\\192.168.2.52\HPPrinter</t>
-  </si>
-  <si>
-    <t>Vinayak</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Time Zone</t>
-  </si>
-  <si>
-    <t>Time Server</t>
-  </si>
-  <si>
-    <t>Date Time</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>(UTC+05:30) Chennai, Kolkata, Mumbai, New Delhi</t>
-  </si>
-  <si>
-    <t>time.nist.gov</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Format</t>
-  </si>
-  <si>
-    <t>Date Separator</t>
-  </si>
-  <si>
-    <t>Short Date Format</t>
-  </si>
-  <si>
-    <t>Long Date Format</t>
-  </si>
-  <si>
-    <t>Time Format</t>
-  </si>
-  <si>
-    <t>Region &amp; Location</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>English - India</t>
-  </si>
-  <si>
-    <t>Date &amp; Time Format</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>dd/MMM/yy</t>
-  </si>
-  <si>
-    <t>dddd, dd MMMM, yyyy</t>
-  </si>
-  <si>
-    <t>h:mm:ss tt</t>
-  </si>
-  <si>
-    <t>Application Path</t>
-  </si>
-  <si>
-    <t>Parameters</t>
-  </si>
-  <si>
-    <t>AlertUser</t>
-  </si>
-  <si>
-    <t>Message Type</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Message</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Required Command Output</t>
-  </si>
-  <si>
-    <t>Timeout</t>
-  </si>
-  <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>C:\Windows\System32\mmc.exe</t>
-  </si>
-  <si>
-    <t>testdata parameters</t>
-  </si>
-  <si>
-    <t>Message box</t>
-  </si>
-  <si>
-    <t>test title</t>
-  </si>
-  <si>
-    <t>test message</t>
-  </si>
-  <si>
-    <t>2 Minute</t>
-  </si>
-  <si>
-    <t>C:\Windows\System32\cleanmgr.exe</t>
-  </si>
-  <si>
-    <t>Information message box</t>
-  </si>
-  <si>
-    <t>1 Minute</t>
-  </si>
-  <si>
-    <t>getmac</t>
-  </si>
-  <si>
-    <t>ipconfig</t>
-  </si>
-  <si>
-    <t>5 Seconds</t>
-  </si>
-  <si>
-    <t>Variable Name</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>test variable</t>
-  </si>
-  <si>
-    <t>Browser Installed</t>
-  </si>
-  <si>
-    <t>Forcefully Close The Browser Instance</t>
-  </si>
-  <si>
-    <t>Internet Browser Cookies</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Temporary Internet Files</t>
-  </si>
-  <si>
-    <t>Clear The Recent Document History</t>
-  </si>
-  <si>
-    <t>Clear The Start Menu Run History</t>
-  </si>
-  <si>
-    <t>Clear The Find Files History</t>
-  </si>
-  <si>
-    <t>Clear The MS Paint Recent File History</t>
-  </si>
-  <si>
-    <t>Clear The MS Wordpad Recent File History</t>
-  </si>
-  <si>
-    <t>Clear The Command Dialogue Open Save History</t>
-  </si>
-  <si>
-    <t>Clear The Command Dialogue Last Visited Folder History</t>
-  </si>
-  <si>
-    <t>Please Empty The Clipboard</t>
-  </si>
-  <si>
-    <t>Empty The Recycle Bin</t>
-  </si>
-  <si>
-    <t>Delete Windows Temporary Files</t>
-  </si>
-  <si>
-    <t>Web Browser</t>
-  </si>
-  <si>
-    <t>Google Chrome</t>
-  </si>
-  <si>
-    <t>Internet Explorer</t>
-  </si>
-  <si>
-    <t>Windows Cleaner</t>
-  </si>
-  <si>
-    <t>Registry Key User</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Backup Path</t>
-  </si>
-  <si>
-    <t>Backup Name</t>
-  </si>
-  <si>
-    <t>Obtain Registry</t>
-  </si>
-  <si>
-    <t>HKEY_USERS</t>
-  </si>
-  <si>
-    <t>WOW6432Node\RemoteApps\RemoteSettings</t>
-  </si>
-  <si>
-    <t>Registry Backup</t>
-  </si>
-  <si>
-    <t>C:\</t>
-  </si>
-  <si>
-    <t>demo backup</t>
-  </si>
-  <si>
-    <t>Application Name</t>
-  </si>
-  <si>
-    <t>isEnabled</t>
-  </si>
-  <si>
-    <t>C:\Windows\System32\cmd.exe</t>
-  </si>
-  <si>
-    <t>cmd.exe</t>
-  </si>
-  <si>
-    <t>C:\Windows\System32\notepad.exe</t>
-  </si>
-  <si>
-    <t>notepad.exe</t>
-  </si>
-  <si>
-    <t>Task Name</t>
-  </si>
-  <si>
-    <t>Delete</t>
-  </si>
-  <si>
-    <t>Refresh</t>
-  </si>
-  <si>
-    <t>MicrosoftEdgeUpdateTaskMachineCore</t>
-  </si>
-  <si>
-    <t>Task Reboot Monitoring</t>
-  </si>
-  <si>
-    <t>DHCP Discovery</t>
-  </si>
-  <si>
-    <t>Monitoring and Maintainance</t>
-  </si>
-  <si>
-    <t>Battery Indicator</t>
-  </si>
-  <si>
-    <t>Idle State</t>
-  </si>
-  <si>
-    <t>Config Sync</t>
-  </si>
-  <si>
-    <t>BootLog</t>
-  </si>
-  <si>
-    <t>Usb Mass Storage Logs</t>
-  </si>
-  <si>
-    <t>Screen Saver Logs</t>
-  </si>
-  <si>
-    <t>Enable Vnc Acceptance</t>
-  </si>
-  <si>
-    <t>Sync Task Scheduler</t>
-  </si>
-  <si>
-    <t>Application Log</t>
-  </si>
-  <si>
-    <t>Cpu Utilization Log</t>
-  </si>
-  <si>
-    <t>Write Filter Logs</t>
-  </si>
-  <si>
-    <t>SignalR Monitoring</t>
-  </si>
-  <si>
-    <t>Hardware Logs</t>
-  </si>
-  <si>
-    <t>Enable Agent Debug Logs</t>
-  </si>
-  <si>
-    <t>Download Attempts</t>
-  </si>
-  <si>
-    <t>Location Range</t>
-  </si>
-  <si>
-    <t>Hardware Logs Interval</t>
-  </si>
-  <si>
-    <t>Heart Beat Interval</t>
-  </si>
-  <si>
-    <t>SignalR Connection Path</t>
-  </si>
-  <si>
-    <t>User Level</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>/communication/signalr/hubs</t>
-  </si>
-  <si>
-    <t>Developer Level</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>VNC Password</t>
-  </si>
-  <si>
-    <t>Server IP Name</t>
-  </si>
-  <si>
-    <t>Port Number</t>
-  </si>
-  <si>
-    <t>winserver.vdi.com</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>Startup Type</t>
-  </si>
-  <si>
-    <t>Microsoft App-V Client</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>Automatic</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>RESTART</t>
-  </si>
-  <si>
-    <t>STOP</t>
-  </si>
-  <si>
-    <t>USB Device Controller Status</t>
-  </si>
-  <si>
-    <t>Audio</t>
-  </si>
-  <si>
-    <t>Audio/Video</t>
-  </si>
-  <si>
-    <t>Human Interface</t>
-  </si>
-  <si>
-    <t>Image Devices</t>
-  </si>
-  <si>
-    <t>Mass Storage</t>
-  </si>
-  <si>
-    <t>Printers</t>
-  </si>
-  <si>
-    <t>Smart Card Reader</t>
-  </si>
-  <si>
-    <t>Video</t>
-  </si>
-  <si>
-    <t>Wireless Controllers</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Member Of</t>
-  </si>
-  <si>
-    <t>User Can Not Change The Password</t>
-  </si>
-  <si>
-    <t>Password Never Expires</t>
-  </si>
-  <si>
-    <t>Disable User</t>
-  </si>
-  <si>
-    <t>Add User</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>admin@123</t>
-  </si>
-  <si>
-    <t>Admin Admin</t>
-  </si>
-  <si>
-    <t>testdata description</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Reset User</t>
-  </si>
-  <si>
-    <t>000000</t>
-  </si>
-  <si>
-    <t>Write Filter Setting</t>
-  </si>
-  <si>
-    <t>Write Filter</t>
-  </si>
-  <si>
-    <t>File And Folder Path</t>
-  </si>
-  <si>
-    <t>Registry Path</t>
-  </si>
-  <si>
-    <t>Set Max Cache Size For Next Session</t>
-  </si>
-  <si>
-    <t>Overlay Size</t>
-  </si>
-  <si>
-    <t>Alert User</t>
-  </si>
-  <si>
-    <t>Message Important</t>
-  </si>
-  <si>
-    <t>Disable Write Filter</t>
-  </si>
-  <si>
-    <t>Write Filter Exclusion List</t>
-  </si>
-  <si>
-    <t>Enable UWF</t>
-  </si>
-  <si>
-    <t>HKEY_LOCAL_MACHINE\SOFTWARE\policies\chrome</t>
-  </si>
-  <si>
-    <t>Information</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>Message from Administrator</t>
-  </si>
-  <si>
-    <t>A maintenance task is going to be performed on your desktop. Your device may Shutdown to complete the task, so you need to save any open work to avoid data loss and then press ok</t>
-  </si>
-  <si>
-    <t>FBWF Cache Size</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Overlay Settings</t>
-  </si>
-  <si>
-    <t>Select New Install Or Uninstall</t>
-  </si>
-  <si>
-    <t>Source Type</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>File Name</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Global Repository</t>
-  </si>
-  <si>
-    <t>NEW INSTALL</t>
-  </si>
-  <si>
-    <t>Repository</t>
-  </si>
-  <si>
-    <t>FDM_HTTP</t>
-  </si>
-  <si>
-    <t>ChromeSetup.exe</t>
-  </si>
-  <si>
-    <t>/quiet</t>
-  </si>
-  <si>
-    <t>New Upload</t>
+    <t>//192.169.1.1/TestPrinter</t>
   </si>
   <si>
     <t>HTTPS</t>
   </si>
   <si>
-    <t>$Group$</t>
-  </si>
-  <si>
-    <t>$GROUP$</t>
-  </si>
-  <si>
     <t>AnyDesk.exe</t>
-  </si>
-  <si>
-    <t>Select Protocol</t>
-  </si>
-  <si>
-    <t>Program Name</t>
-  </si>
-  <si>
-    <t>Program Path</t>
-  </si>
-  <si>
-    <t>Add Port</t>
-  </si>
-  <si>
-    <t>TcpPort</t>
-  </si>
-  <si>
-    <t>TCP</t>
-  </si>
-  <si>
-    <t>UdpPort</t>
-  </si>
-  <si>
-    <t>UDP</t>
-  </si>
-  <si>
-    <t>Add Program</t>
-  </si>
-  <si>
-    <t>testprogramname</t>
-  </si>
-  <si>
-    <t>C:\Program Files\Internet Explorer\iexplore.exe</t>
-  </si>
-  <si>
-    <t>Automatically Detect Settings</t>
-  </si>
-  <si>
-    <t>Use Automatic Configuration Script</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Installation &amp; Uninstallation Restriction</t>
-  </si>
-  <si>
-    <t>Software Restriction</t>
-  </si>
-  <si>
-    <t>Software Application  Name</t>
-  </si>
-  <si>
-    <t>Browser Name</t>
-  </si>
-  <si>
-    <t>Restriction Type</t>
-  </si>
-  <si>
-    <t>Installation &amp; Uninstallation</t>
-  </si>
-  <si>
-    <t>Application Restriction</t>
-  </si>
-  <si>
-    <t>Allow All</t>
-  </si>
-  <si>
-    <t>Deny All</t>
-  </si>
-  <si>
-    <t>Browser Restriction</t>
-  </si>
-  <si>
-    <t>Block all downloads</t>
-  </si>
-  <si>
-    <t>File Folder</t>
-  </si>
-  <si>
-    <t>C:\Users\Administrator\Desktop</t>
-  </si>
-  <si>
-    <t>ConnectionName</t>
-  </si>
-  <si>
-    <t>Certificate Type</t>
-  </si>
-  <si>
-    <t>Store Name</t>
-  </si>
-  <si>
-    <t>File</t>
-  </si>
-  <si>
-    <t>CER</t>
-  </si>
-  <si>
-    <t>ShradhaCerFile.cer</t>
-  </si>
-  <si>
-    <t>Personal certificates</t>
-  </si>
-  <si>
-    <t>FTPS</t>
-  </si>
-  <si>
-    <t>PFX</t>
-  </si>
-  <si>
-    <t>ShradhaPexFile.pfx</t>
-  </si>
-  <si>
-    <t>Trusted Publishers</t>
-  </si>
-  <si>
-    <t>Enable CD DVD</t>
-  </si>
-  <si>
-    <t>Bluetooth Device</t>
-  </si>
-  <si>
-    <t>Enable</t>
-  </si>
-  <si>
-    <t>Disable</t>
-  </si>
-  <si>
-    <t>Enable Firewall</t>
-  </si>
-  <si>
-    <t>Enable Parallel Port</t>
-  </si>
-  <si>
-    <t>Enable Serial Port</t>
-  </si>
-  <si>
-    <t>Enable USB Port</t>
-  </si>
-  <si>
-    <t>USB Mass Storage</t>
-  </si>
-  <si>
-    <t>USB Write Protect</t>
-  </si>
-  <si>
-    <t>testingpr1</t>
-  </si>
-  <si>
-    <t>testingpr2</t>
-  </si>
-  <si>
-    <t>demo postponement message</t>
-  </si>
-  <si>
-    <t>testingpr3</t>
-  </si>
-  <si>
-    <t>Asynchronous</t>
-  </si>
-  <si>
-    <t>testingpr4</t>
-  </si>
-  <si>
-    <t>testingpr5</t>
-  </si>
-  <si>
-    <t>Linux</t>
-  </si>
-  <si>
-    <t>testingpr6</t>
-  </si>
-  <si>
-    <t>testingpr7</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>testingpr8</t>
-  </si>
-  <si>
-    <t>testingpr9</t>
-  </si>
-  <si>
-    <t>IOS</t>
-  </si>
-  <si>
-    <t>testingpr10</t>
-  </si>
-  <si>
-    <t>//192.169.1.1/TestPrinter</t>
-  </si>
-  <si>
-    <t>Connection Name</t>
-  </si>
-  <si>
-    <t>Citrix Type</t>
-  </si>
-  <si>
-    <t>Configuration URL</t>
-  </si>
-  <si>
-    <t>testConnection</t>
-  </si>
-  <si>
-    <t>Store</t>
-  </si>
-  <si>
-    <t>testStore</t>
-  </si>
-  <si>
-    <t>https://xd711.vdi.com</t>
-  </si>
-  <si>
-    <t>testDescription</t>
-  </si>
-  <si>
-    <t>PNA</t>
-  </si>
-  <si>
-    <t>https://192.168.1.23/Citrix/PNAgent/Config.xml</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Create Shortcut On Desktop</t>
-  </si>
-  <si>
-    <t>Auto Start Connection</t>
-  </si>
-  <si>
-    <t>Arguments</t>
-  </si>
-  <si>
-    <t>C:\Applications\AppBusiness.exe</t>
-  </si>
-  <si>
-    <t>testArguments</t>
-  </si>
-  <si>
-    <t>Browser Type</t>
-  </si>
-  <si>
-    <t>Kiosk Mode</t>
-  </si>
-  <si>
-    <t>Auto Reconnect Connection</t>
-  </si>
-  <si>
-    <t>Chrome</t>
-  </si>
-  <si>
-    <t>http://www.google.com</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>IP Host Name</t>
-  </si>
-  <si>
-    <t>Always Ask For Cred</t>
-  </si>
-  <si>
-    <t>Automatic Start</t>
-  </si>
-  <si>
-    <t>Use All Monitors For Remote Session</t>
-  </si>
-  <si>
-    <t>Full Screen</t>
-  </si>
-  <si>
-    <t>Size Of Desktop</t>
-  </si>
-  <si>
-    <t>Colors</t>
-  </si>
-  <si>
-    <t>Display Connection Bar</t>
-  </si>
-  <si>
-    <t>Remote Audio Playback</t>
-  </si>
-  <si>
-    <t>Remote Audio Recording</t>
-  </si>
-  <si>
-    <t>Drives</t>
-  </si>
-  <si>
-    <t>Clipboard</t>
-  </si>
-  <si>
-    <t>Smart Cards</t>
-  </si>
-  <si>
-    <t>Ports</t>
-  </si>
-  <si>
-    <t>PNP Devices</t>
-  </si>
-  <si>
-    <t>Keyboard</t>
-  </si>
-  <si>
-    <t>Program Path File Name</t>
-  </si>
-  <si>
-    <t>Start In Following Folder</t>
-  </si>
-  <si>
-    <t>Connection Speed</t>
-  </si>
-  <si>
-    <t>Reconnect If Connection Dropped</t>
-  </si>
-  <si>
-    <t>Authentication Option</t>
-  </si>
-  <si>
-    <t>Do Not Use RD Gateway</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Automatic Logon</t>
-  </si>
-  <si>
-    <t>192.168.3.138</t>
-  </si>
-  <si>
-    <t>Start Program On Connection</t>
-  </si>
-  <si>
-    <t>vdi.com</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>1024x768</t>
-  </si>
-  <si>
-    <t>High Color(16 bit)</t>
-  </si>
-  <si>
-    <t>True Color(24 bit)</t>
-  </si>
-  <si>
-    <t>Local Resources</t>
-  </si>
-  <si>
-    <t>Do not play</t>
-  </si>
-  <si>
-    <t>Do not record</t>
-  </si>
-  <si>
-    <t>On the remote computer</t>
-  </si>
-  <si>
-    <t>Programs</t>
-  </si>
-  <si>
-    <t>D:\sample\sample.exe</t>
-  </si>
-  <si>
-    <t>Experience</t>
-  </si>
-  <si>
-    <t>LAN(10 Mbps or higher)</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>Warn me</t>
-  </si>
-  <si>
-    <t>Host Name</t>
-  </si>
-  <si>
-    <t>Remote work station card</t>
-  </si>
-  <si>
-    <t>Usb Disable</t>
-  </si>
-  <si>
-    <t>Create Shortcut in the start menu</t>
-  </si>
-  <si>
-    <t>Teradici PCoIP</t>
-  </si>
-  <si>
-    <t>vdi</t>
-  </si>
-  <si>
-    <t>Windowed</t>
-  </si>
-  <si>
-    <t>Fullscreen</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>Application or Desktop Name</t>
-  </si>
-  <si>
-    <t>Smart Card Pin</t>
-  </si>
-  <si>
-    <t>Connect Usb On Startup</t>
-  </si>
-  <si>
-    <t>Connect Usb On Insert</t>
-  </si>
-  <si>
-    <t>Non Interactive</t>
-  </si>
-  <si>
-    <t>Reconnect Behaviour</t>
-  </si>
-  <si>
-    <t>VMW Protocol</t>
-  </si>
-  <si>
-    <t>Desktop Name</t>
-  </si>
-  <si>
-    <t>chrome.exe</t>
-  </si>
-  <si>
-    <t>Reconnect automatically to open applications</t>
-  </si>
-  <si>
-    <t>RDP protocol setting</t>
-  </si>
-  <si>
-    <t>PDF Viewer</t>
-  </si>
-  <si>
-    <t>Citrix Workspace</t>
-  </si>
-  <si>
-    <t>Unauthenticated Access</t>
-  </si>
-  <si>
-    <t>Hide Client After Launch</t>
-  </si>
-  <si>
-    <t>Allow H264 Decoding</t>
-  </si>
-  <si>
-    <t>Allow High Color Accuracy</t>
-  </si>
-  <si>
-    <t>Configure SSL</t>
-  </si>
-  <si>
-    <t>Network Condition</t>
-  </si>
-  <si>
-    <t>Never connect to untrusted server</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>Do not verify server identity certificates</t>
-  </si>
-  <si>
-    <t>Poor</t>
-  </si>
-  <si>
-    <t>Disable Client Save</t>
-  </si>
-  <si>
-    <t>Lock Computer Save</t>
-  </si>
-  <si>
-    <t>Importance</t>
-  </si>
-  <si>
-    <t>Feedback</t>
-  </si>
-  <si>
-    <t>Message from prajwal</t>
-  </si>
-  <si>
-    <t>5 Minute</t>
-  </si>
-  <si>
-    <t>Disabled Service Mode</t>
-  </si>
-  <si>
-    <t>Service Mode</t>
-  </si>
-  <si>
-    <t>Enabled Service Mode</t>
-  </si>
-  <si>
-    <t>Shut Down</t>
-  </si>
-  <si>
-    <t>Inventory Sync</t>
-  </si>
-  <si>
-    <t>Hardware &amp; Software Inventory(Windows)</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Wake On Lan Save</t>
-  </si>
-  <si>
-    <t>Target Folder Path</t>
-  </si>
-  <si>
-    <t>Execute File</t>
-  </si>
-  <si>
-    <t>Batch Execution</t>
-  </si>
-  <si>
-    <t>Command Parameter</t>
-  </si>
-  <si>
-    <t>File Transfer</t>
-  </si>
-  <si>
-    <t>Upload</t>
-  </si>
-  <si>
-    <t>test command</t>
-  </si>
-  <si>
-    <t>Folder Transfer</t>
-  </si>
-  <si>
-    <t>sample-1.zip</t>
-  </si>
-  <si>
-    <t>File Path</t>
-  </si>
-  <si>
-    <t>Folder Path</t>
-  </si>
-  <si>
-    <t>Folder Synchronization Path</t>
-  </si>
-  <si>
-    <t>Import File</t>
-  </si>
-  <si>
-    <t>C:\Test.txt</t>
-  </si>
-  <si>
-    <t>Import Folder</t>
-  </si>
-  <si>
-    <t>C:\MyFolder</t>
-  </si>
-  <si>
-    <t>Folder synchronization</t>
-  </si>
-  <si>
-    <t>C:\Program Files (x86)\LogsDir\DeveloperLog.log</t>
-  </si>
-  <si>
-    <t>C:\Program Files (x86)\LogsDir\Connections</t>
-  </si>
-  <si>
-    <t>FolderTransferFiles.zip</t>
-  </si>
-  <si>
-    <t>2XClient.msi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1741,9 +1735,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1754,23 +1748,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2070,68 +2058,68 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2142,7 +2130,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2168,22 +2156,22 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -2210,43 +2198,43 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="str">
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D2" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="str">
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="9" customFormat="1">
-      <c r="A2" s="8" t="str">
-        <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="9" customFormat="1">
-      <c r="A3" s="8" t="str">
-        <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>111</v>
+      <c r="D3" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2278,56 +2266,56 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="G2" s="1" t="s">
         <v>26</v>
       </c>
@@ -2341,28 +2329,28 @@
         <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>26</v>
@@ -2383,25 +2371,25 @@
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H4" s="1">
         <v>92000</v>
@@ -2416,40 +2404,40 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="9" customFormat="1">
-      <c r="A5" s="8" t="str">
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>44</v>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2480,34 +2468,34 @@
         <v>50</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1">
         <v>2025</v>
@@ -2515,8 +2503,8 @@
       <c r="E2" s="1">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>138</v>
+      <c r="F2" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>26</v>
@@ -2528,10 +2516,10 @@
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>26</v>
@@ -2546,7 +2534,7 @@
         <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>26</v>
@@ -2555,10 +2543,10 @@
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
@@ -2576,7 +2564,7 @@
         <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2607,42 +2595,42 @@
         <v>50</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -2655,28 +2643,28 @@
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2700,7 +2688,7 @@
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
     </row>
   </sheetData>
@@ -2736,198 +2724,198 @@
         <v>50</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="9" customFormat="1">
-      <c r="A2" s="8" t="str">
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="8" t="s">
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="H2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="I2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="J2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="str">
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="E3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="G3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="9" customFormat="1">
-      <c r="A3" s="8" t="str">
+      <c r="H3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="8" t="s">
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="K4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="str">
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8" t="s">
+      <c r="K5" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="9" customFormat="1">
-      <c r="A4" s="8" t="str">
-        <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="L5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="9" customFormat="1">
-      <c r="A5" s="8" t="str">
-        <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2956,22 +2944,22 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>165</v>
+        <v>177</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3011,73 +2999,73 @@
         <v>50</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>26</v>
@@ -3113,25 +3101,25 @@
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>26</v>
@@ -3167,10 +3155,10 @@
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
@@ -3188,34 +3176,34 @@
         <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3245,58 +3233,58 @@
         <v>50</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3312,12 +3300,12 @@
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="9" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" customWidth="1"/>
     <col min="7" max="7" width="24.42578125" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="9" customWidth="1"/>
     <col min="9" max="9" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3328,7 +3316,7 @@
       <c r="B1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -3346,7 +3334,7 @@
       <c r="H1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3401,42 +3389,42 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="8" t="s">
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>44</v>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B3" s="8" t="s">
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3461,25 +3449,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -3527,154 +3515,154 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="T2" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="U2" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="V2" s="1">
         <v>6</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -3689,61 +3677,61 @@
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="T3" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="U3" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="U3" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="V3" s="1">
         <v>6</v>
       </c>
-      <c r="W3" s="14" t="s">
-        <v>247</v>
+      <c r="W3" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3765,13 +3753,13 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1">
         <v>111111</v>
@@ -3780,7 +3768,7 @@
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -3807,22 +3795,22 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="D1" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C2" s="1">
         <v>443</v>
@@ -3853,13 +3841,13 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>15</v>
@@ -3868,34 +3856,34 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -3904,31 +3892,31 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>26</v>
@@ -3940,19 +3928,19 @@
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3983,91 +3971,91 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>24</v>
@@ -4114,85 +4102,85 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
@@ -4207,16 +4195,16 @@
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>285</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -4275,37 +4263,37 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>21</v>
@@ -4314,13 +4302,13 @@
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -4359,55 +4347,55 @@
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
@@ -4428,31 +4416,31 @@
         <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="L4" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>26</v>
@@ -4498,7 +4486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4519,37 +4507,37 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="D2" s="1">
         <v>8765</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>26</v>
@@ -4561,19 +4549,19 @@
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="D3" s="1">
         <v>4433</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -4585,10 +4573,10 @@
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
@@ -4600,10 +4588,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4667,7 +4655,7 @@
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -4685,25 +4673,25 @@
         <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>38</v>
@@ -4715,31 +4703,31 @@
         <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>38</v>
@@ -4757,25 +4745,25 @@
         <v>41</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
@@ -4799,22 +4787,25 @@
         <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4829,19 +4820,19 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
@@ -4859,7 +4850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4880,31 +4871,31 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -4922,19 +4913,19 @@
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>469</v>
+        <v>327</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -4946,19 +4937,19 @@
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>470</v>
+        <v>329</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
@@ -4970,10 +4961,10 @@
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>26</v>
@@ -4985,10 +4976,10 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4997,7 +4988,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5010,16 +5001,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5028,7 +5019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5047,46 +5038,46 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A8" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>26</v>
@@ -5098,25 +5089,25 @@
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>26</v>
@@ -5125,25 +5116,25 @@
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>26</v>
@@ -5152,118 +5143,118 @@
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-2100-000000000000}"/>
-    <hyperlink ref="G6" r:id="rId2" xr:uid="{00000000-0004-0000-2100-000001000000}"/>
-    <hyperlink ref="G7" r:id="rId3" xr:uid="{00000000-0004-0000-2100-000002000000}"/>
-    <hyperlink ref="G8" r:id="rId4" xr:uid="{00000000-0004-0000-2100-000003000000}"/>
-    <hyperlink ref="G3" r:id="rId5" xr:uid="{0421A459-F154-4D79-9639-94FC8E6EC1FD}"/>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-2000-000000000000}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{00000000-0004-0000-2000-000001000000}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{00000000-0004-0000-2000-000002000000}"/>
+    <hyperlink ref="G8" r:id="rId4" xr:uid="{00000000-0004-0000-2000-000003000000}"/>
+    <hyperlink ref="G3" r:id="rId5" xr:uid="{00000000-0004-0000-2000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5271,7 +5262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5285,40 +5276,40 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A4" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>26</v>
@@ -5334,7 +5325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5353,58 +5344,58 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -5416,16 +5407,16 @@
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5434,16 +5425,16 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34BEC3E4-E5E1-433E-AD96-E993DB0F10E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5451,83 +5442,82 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{87B21DC9-1E36-444F-8624-9C95AC9DDC04}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{62F87EB5-46FC-42F9-AE82-429E6A70652D}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-2300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DF793F-8BC4-4006-8A55-542F8FEBAF7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5535,61 +5525,61 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>400</v>
+        <v>161</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>401</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -5598,18 +5588,18 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9CF9A1-DEC6-4E65-B8D9-9D889BEE77EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5617,67 +5607,67 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -5689,55 +5679,55 @@
         <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{1FD35AC0-8A6A-407C-B9E8-E5ED61273878}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00786D6F-BCD0-4EE6-A8A3-61B1E4E8B9E9}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-2500-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" tooltip="http://www.gmail.com" xr:uid="{00000000-0004-0000-2500-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8B2B7-7CA9-4C4B-9B22-221B73EA37BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:AF10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="23" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="34.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="22.28515625" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" customWidth="1"/>
+    <col min="21" max="21" width="8" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" customWidth="1"/>
+    <col min="23" max="23" width="5.5703125" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="23.42578125" customWidth="1"/>
+    <col min="26" max="26" width="27.140625" customWidth="1"/>
+    <col min="27" max="27" width="22.7109375" customWidth="1"/>
+    <col min="28" max="28" width="23" customWidth="1"/>
+    <col min="29" max="29" width="22.140625" customWidth="1"/>
+    <col min="30" max="30" width="31.42578125" customWidth="1"/>
+    <col min="31" max="31" width="21.140625" customWidth="1"/>
+    <col min="32" max="32" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -5745,22 +5735,22 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>68</v>
@@ -5769,100 +5759,100 @@
         <v>1</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>431</v>
+        <v>391</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="AD1" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>412</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A10" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="E2" s="1">
         <v>4455</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>434</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>26</v>
@@ -5940,16 +5930,16 @@
     <row r="3" spans="1:32">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="E3" s="1">
         <v>4455</v>
@@ -5958,19 +5948,19 @@
         <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>434</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>26</v>
@@ -6039,16 +6029,16 @@
     <row r="4" spans="1:32">
       <c r="A4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -6078,10 +6068,10 @@
         <v>24</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>24</v>
@@ -6138,16 +6128,16 @@
     <row r="5" spans="1:32">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>26</v>
@@ -6171,7 +6161,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>26</v>
@@ -6180,10 +6170,10 @@
         <v>26</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>26</v>
@@ -6237,16 +6227,16 @@
     <row r="6" spans="1:32">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
@@ -6285,31 +6275,31 @@
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
@@ -6334,16 +6324,16 @@
     <row r="7" spans="1:32">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
@@ -6433,16 +6423,16 @@
     <row r="8" spans="1:32">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
@@ -6508,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>26</v>
@@ -6532,16 +6522,16 @@
     <row r="9" spans="1:32">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>26</v>
@@ -6616,7 +6606,7 @@
         <v>26</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>26</v>
@@ -6631,16 +6621,16 @@
     <row r="10" spans="1:32">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
@@ -6721,19 +6711,19 @@
         <v>26</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="prajwal@vdi.com" xr:uid="{5100CE7D-5248-4F70-9865-1B61E7AB9DA9}"/>
-    <hyperlink ref="H3" r:id="rId2" display="prajwal@vdi.com" xr:uid="{50CEEA5D-E759-4F05-B140-4B22E66D6D0F}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-2600-000000000000}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-2600-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -6775,7 +6765,7 @@
       <c r="B1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -6793,7 +6783,7 @@
       <c r="H1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>57</v>
       </c>
       <c r="J1" s="7" t="s">
@@ -6821,7 +6811,7 @@
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -6836,7 +6826,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>66</v>
@@ -6872,7 +6862,7 @@
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>68</v>
@@ -6899,16 +6889,16 @@
         <v>68</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>26</v>
@@ -6923,7 +6913,7 @@
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>68</v>
@@ -6947,7 +6937,7 @@
         <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>26</v>
@@ -6962,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6978,22 +6968,22 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C85BBD-E301-4B30-9FF9-BA00C2199C89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -7001,34 +6991,34 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>53</v>
@@ -7037,61 +7027,61 @@
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>24</v>
@@ -7100,16 +7090,16 @@
         <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -7118,27 +7108,27 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17A79F0-B263-4E61-8CAF-743040795E27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="42.28515625" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -7146,13 +7136,13 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -7164,115 +7154,115 @@
         <v>53</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="I2" s="1">
         <v>2000</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="I3" s="1">
         <v>2000</v>
@@ -7281,45 +7271,45 @@
         <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C7C9D1-B1C6-4779-843D-3E1066D897DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7327,52 +7317,52 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -7387,10 +7377,10 @@
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -7399,12 +7389,12 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589242E6-89E1-4CF1-B175-9A33B7D61751}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7412,16 +7402,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -7430,12 +7420,12 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BCCE91-3E04-4E68-A502-564F866F8581}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7443,16 +7433,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7461,12 +7451,12 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416F9061-7B84-4B25-A46A-D44F915B18A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7474,16 +7464,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7492,12 +7482,12 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1B9DE4-3151-4432-9050-7A575CBAECD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7505,16 +7495,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7523,17 +7513,17 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0B3002-D4BA-43F4-B58D-44D7D7E96CE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7541,46 +7531,46 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>486</v>
+        <v>171</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7589,12 +7579,12 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBA058F-608D-4D6F-B80F-3867385F0F21}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7602,43 +7592,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
-        <f t="shared" ref="A2:A5" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -7647,12 +7619,12 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8495A8D-3D6D-4F6B-8682-A2EE450B8100}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7660,16 +7632,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -7695,28 +7667,28 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -7728,19 +7700,19 @@
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -7749,12 +7721,12 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E464DC-FA47-4F2C-8724-594CCBF1CB82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7762,40 +7734,40 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A3" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>492</v>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>493</v>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA31968F-3F48-4A6C-9F66-029EF92AC4A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7803,16 +7775,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>44</v>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7821,21 +7793,21 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7061B5F3-05D1-4501-AA21-73D88B847832}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7846,100 +7818,100 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>311</v>
+        <v>475</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A4" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>512</v>
+        <v>206</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
@@ -7948,34 +7920,34 @@
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>26</v>
@@ -7987,17 +7959,17 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE172099-6B99-469B-9DF2-B9AA73956E7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3400-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8008,37 +7980,37 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="str">
         <f t="shared" ref="A2:A6" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>26</v>
@@ -8050,19 +8022,19 @@
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -8074,22 +8046,22 @@
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>26</v>
@@ -8098,13 +8070,13 @@
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>26</v>
@@ -8113,7 +8085,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
@@ -8122,10 +8094,10 @@
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>26</v>
@@ -8140,7 +8112,7 @@
         <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -8149,7 +8121,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3500-000000000000}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -8168,106 +8140,106 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>306</v>
+        <v>494</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>310</v>
+        <v>495</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>311</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>499</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8276,13 +8248,13 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3600-000000000000}">
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>23</v>
@@ -8335,7 +8307,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -8364,13 +8336,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>371</v>
+        <v>501</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>25</v>
@@ -8379,7 +8351,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>372</v>
+        <v>502</v>
       </c>
       <c r="G7" s="2">
         <v>2</v>
@@ -8393,7 +8365,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>373</v>
+        <v>503</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -8402,13 +8374,13 @@
         <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>374</v>
+        <v>504</v>
       </c>
       <c r="E8" s="2">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>372</v>
+        <v>502</v>
       </c>
       <c r="G8" s="2">
         <v>13</v>
@@ -8422,16 +8394,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>375</v>
+        <v>505</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>374</v>
+        <v>504</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -8451,10 +8423,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>376</v>
+        <v>506</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>507</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -8480,16 +8452,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>378</v>
+        <v>508</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>377</v>
+        <v>507</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>374</v>
+        <v>504</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>26</v>
@@ -8509,10 +8481,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>379</v>
+        <v>509</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>380</v>
+        <v>510</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>26</v>
@@ -8538,16 +8510,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>381</v>
+        <v>511</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>380</v>
+        <v>510</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>374</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>26</v>
@@ -8567,10 +8539,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>382</v>
+        <v>512</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>383</v>
+        <v>513</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>26</v>
@@ -8596,16 +8568,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>384</v>
+        <v>514</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>383</v>
+        <v>513</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>374</v>
+        <v>504</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
@@ -8669,22 +8641,22 @@
         <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>515</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8698,25 +8670,25 @@
         <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8733,22 +8705,22 @@
         <v>48</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>41</v>
+        <v>515</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8774,34 +8746,34 @@
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="G25" s="1" t="s">
         <v>26</v>
       </c>
@@ -8815,27 +8787,27 @@
         <v>26</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>26</v>
@@ -8855,25 +8827,25 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H27" s="1">
         <v>92000</v>
@@ -8890,13 +8862,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>385</v>
+        <v>516</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>26</v>
@@ -8914,13 +8886,13 @@
         <v>26</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -8928,74 +8900,74 @@
         <v>13</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>306</v>
+        <v>494</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>310</v>
+        <v>495</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>311</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>318</v>
+        <v>517</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>24</v>
@@ -9003,56 +8975,65 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>319</v>
+        <v>499</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>321</v>
+        <v>518</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="str">
         <f t="shared" ref="A36" si="0">MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3700-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -9075,7 +9056,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>28</v>
@@ -9084,36 +9065,36 @@
         <v>31</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="str">
+        <f>MasterTemplate</f>
+        <v>A102_UEM_Automation_Template</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="9" customFormat="1">
-      <c r="A2" s="8" t="str">
-        <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9143,16 +9124,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -9177,31 +9158,31 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
@@ -9210,37 +9191,37 @@
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -9264,31 +9245,31 @@
         <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="str">
         <f>MasterTemplate</f>
-        <v>A101_UEM_Automation_Template</v>
+        <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
@@ -9300,6 +9281,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bede5cfa-631d-4fd3-b0c4-59605dda9e90" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EFE392A59B870547B1C3C655506A654E" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c5dcf9363f032dfeeb11d9ad86bb7b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bede5cfa-631d-4fd3-b0c4-59605dda9e90" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d394e0e01a44c6ec4efd03b5e4dcc17" ns3:_="">
     <xsd:import namespace="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
@@ -9487,47 +9485,44 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bede5cfa-631d-4fd3-b0c4-59605dda9e90" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1115A243-C08D-40EF-8182-B46E18220BEC}">
-  <ds:schemaRefs/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0FBC653-3026-41A1-A0E4-1AA0FF7A869E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0FBC653-3026-41A1-A0E4-1AA0FF7A869E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE7CF42-BD80-4F72-A4A5-E57C8D02DBB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE7CF42-BD80-4F72-A4A5-E57C8D02DBB4}">
-  <ds:schemaRefs/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1115A243-C08D-40EF-8182-B46E18220BEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/main/java/com/uem_automation/qa/testdata/UEM_AUTOMATION_TESTDATA.xlsx
+++ b/src/main/java/com/uem_automation/qa/testdata/UEM_AUTOMATION_TESTDATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - CYBERCORP LIMITED\Projects\intellij-workspace\UEM_AUTOMATION_TESTNG_FRAMEWORK\src\main\java\com\uem_automation\qa\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D5112858B5AB48CE35E55F9A3B3C6A04DE4AEEA9" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7B2351-8842-4E91-BFE8-179D93150EFE}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="113_{9A09458D-6713-4772-A8EE-7EB04E46E8A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{F692DA11-6850-45B0-8B19-10FF6CAFB639}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000" firstSheet="40" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000" firstSheet="47" activeTab="53" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="518">
   <si>
     <t>Email</t>
   </si>
@@ -1072,9 +1072,6 @@
     <t>Deny All</t>
   </si>
   <si>
-    <t>Citrix Workspace</t>
-  </si>
-  <si>
     <t>Browser Restriction</t>
   </si>
   <si>
@@ -1129,9 +1126,6 @@
     <t>Trusted Publishers</t>
   </si>
   <si>
-    <t>FTPS</t>
-  </si>
-  <si>
     <t>Repository</t>
   </si>
   <si>
@@ -1543,9 +1537,6 @@
     <t>FolderTransferFiles.zip</t>
   </si>
   <si>
-    <t>sample-1.zip</t>
-  </si>
-  <si>
     <t>File Path</t>
   </si>
   <si>
@@ -1579,9 +1570,6 @@
     <t>/quiet</t>
   </si>
   <si>
-    <t>2XClient.msi</t>
-  </si>
-  <si>
     <t>$Group$</t>
   </si>
   <si>
@@ -1640,6 +1628,15 @@
   </si>
   <si>
     <t>AnyDesk.exe</t>
+  </si>
+  <si>
+    <t>explorer.exe</t>
+  </si>
+  <si>
+    <t>WebIAS_HTTP</t>
+  </si>
+  <si>
+    <t>VMSAgent.exe</t>
   </si>
 </sst>
 </file>
@@ -4949,7 +4946,7 @@
         <v>328</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>329</v>
+        <v>515</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
@@ -4964,7 +4961,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>26</v>
@@ -4979,7 +4976,7 @@
         <v>195</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -5001,7 +4998,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5010,7 +5007,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5038,25 +5035,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5065,19 +5062,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>26</v>
@@ -5092,19 +5089,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>279</v>
@@ -5119,19 +5116,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>348</v>
+        <v>516</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>279</v>
@@ -5146,25 +5143,25 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5173,25 +5170,25 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>279</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -5200,25 +5197,25 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -5227,25 +5224,25 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>279</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -5276,10 +5273,10 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5288,10 +5285,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5300,10 +5297,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5344,25 +5341,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5442,16 +5439,16 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>272</v>
@@ -5463,19 +5460,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5484,19 +5481,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>371</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5525,19 +5522,19 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5546,19 +5543,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5567,7 +5564,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>161</v>
@@ -5607,25 +5604,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5634,13 +5631,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>42</v>
@@ -5661,13 +5658,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -5735,19 +5732,19 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>112</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>115</v>
@@ -5759,73 +5756,73 @@
         <v>1</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>401</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>267</v>
       </c>
       <c r="V1" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="X1" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>410</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:32">
@@ -5834,13 +5831,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="E2" s="1">
         <v>4455</v>
@@ -5933,13 +5930,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="E3" s="1">
         <v>4455</v>
@@ -6032,10 +6029,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>77</v>
@@ -6068,10 +6065,10 @@
         <v>24</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>24</v>
@@ -6131,10 +6128,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>77</v>
@@ -6170,7 +6167,7 @@
         <v>26</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>42</v>
@@ -6230,10 +6227,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>77</v>
@@ -6275,10 +6272,10 @@
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>42</v>
@@ -6299,7 +6296,7 @@
         <v>42</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
@@ -6327,10 +6324,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>77</v>
@@ -6426,10 +6423,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>77</v>
@@ -6501,10 +6498,10 @@
         <v>42</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>26</v>
@@ -6525,10 +6522,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>77</v>
@@ -6606,7 +6603,7 @@
         <v>26</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>26</v>
@@ -6624,10 +6621,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>77</v>
@@ -6711,7 +6708,7 @@
         <v>26</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>42</v>
@@ -6991,10 +6988,10 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>32</v>
@@ -7006,19 +7003,19 @@
         <v>1</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>433</v>
-      </c>
       <c r="K1" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>53</v>
@@ -7030,13 +7027,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
@@ -7060,7 +7057,7 @@
         <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -7069,13 +7066,13 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -7099,7 +7096,7 @@
         <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -7136,13 +7133,13 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -7154,34 +7151,34 @@
         <v>53</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="O1" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -7190,7 +7187,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>77</v>
@@ -7208,7 +7205,7 @@
         <v>208</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I2" s="1">
         <v>2000</v>
@@ -7223,10 +7220,10 @@
         <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>42</v>
@@ -7235,7 +7232,7 @@
         <v>42</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -7244,7 +7241,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>77</v>
@@ -7259,10 +7256,10 @@
         <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I3" s="1">
         <v>2000</v>
@@ -7280,7 +7277,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>24</v>
@@ -7289,7 +7286,7 @@
         <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -7317,22 +7314,22 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>453</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7353,10 +7350,10 @@
         <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -7377,10 +7374,10 @@
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -7402,7 +7399,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7433,7 +7430,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7464,7 +7461,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7495,7 +7492,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7534,7 +7531,7 @@
         <v>154</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>155</v>
@@ -7546,7 +7543,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7561,7 +7558,7 @@
         <v>298</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>165</v>
@@ -7592,7 +7589,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7601,7 +7598,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7610,7 +7607,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -7632,7 +7629,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7734,7 +7731,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7743,7 +7740,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7752,7 +7749,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -7775,7 +7772,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7801,7 +7798,7 @@
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="45.28515625" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" customWidth="1"/>
@@ -7818,31 +7815,31 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7851,19 +7848,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>206</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
@@ -7878,7 +7875,7 @@
         <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -7887,19 +7884,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>42</v>
@@ -7923,19 +7920,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>42</v>
@@ -7966,7 +7963,7 @@
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.28515625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" customWidth="1"/>
@@ -7980,19 +7977,19 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8001,16 +7998,16 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>26</v>
@@ -8025,16 +8022,16 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -8049,19 +8046,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>26</v>
@@ -8073,10 +8070,10 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>26</v>
@@ -8085,7 +8082,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
@@ -8097,7 +8094,7 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>26</v>
@@ -8112,7 +8109,7 @@
         <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -8128,7 +8125,7 @@
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
@@ -8140,25 +8137,25 @@
         <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8167,19 +8164,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>42</v>
@@ -8194,19 +8191,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>42</v>
@@ -8221,19 +8218,19 @@
         <v>A102_UEM_Automation_Template</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>42</v>
@@ -8254,7 +8251,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>23</v>
@@ -8307,7 +8304,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -8336,7 +8333,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -8351,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G7" s="2">
         <v>2</v>
@@ -8365,7 +8362,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -8374,13 +8371,13 @@
         <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E8" s="2">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G8" s="2">
         <v>13</v>
@@ -8394,7 +8391,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
@@ -8403,7 +8400,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -8423,10 +8420,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -8452,16 +8449,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>26</v>
@@ -8481,10 +8478,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>26</v>
@@ -8510,16 +8507,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>26</v>
@@ -8539,10 +8536,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>26</v>
@@ -8568,16 +8565,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
@@ -8641,7 +8638,7 @@
         <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>45</v>
@@ -8673,7 +8670,7 @@
         <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>45</v>
@@ -8705,7 +8702,7 @@
         <v>48</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>45</v>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>117</v>
@@ -8792,7 +8789,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>117</v>
@@ -8827,7 +8824,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>122</v>
@@ -8862,13 +8859,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>26</v>
@@ -8900,45 +8897,45 @@
         <v>13</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>42</v>
@@ -8949,22 +8946,22 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>42</v>
@@ -8975,22 +8972,22 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>24</v>
@@ -9017,10 +9014,10 @@
         <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -9281,23 +9278,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bede5cfa-631d-4fd3-b0c4-59605dda9e90" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EFE392A59B870547B1C3C655506A654E" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c5dcf9363f032dfeeb11d9ad86bb7b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bede5cfa-631d-4fd3-b0c4-59605dda9e90" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d394e0e01a44c6ec4efd03b5e4dcc17" ns3:_="">
     <xsd:import namespace="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
@@ -9485,31 +9465,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0FBC653-3026-41A1-A0E4-1AA0FF7A869E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bede5cfa-631d-4fd3-b0c4-59605dda9e90" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE7CF42-BD80-4F72-A4A5-E57C8D02DBB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1115A243-C08D-40EF-8182-B46E18220BEC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9525,4 +9498,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0FBC653-3026-41A1-A0E4-1AA0FF7A869E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="bede5cfa-631d-4fd3-b0c4-59605dda9e90"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE7CF42-BD80-4F72-A4A5-E57C8D02DBB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>